--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484217_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484217_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1669</v>
+        <v>6.8327</v>
       </c>
       <c r="E2" t="n">
-        <v>3.543</v>
+        <v>3.664</v>
       </c>
       <c r="F2" t="n">
-        <v>2.624</v>
+        <v>3.1687</v>
       </c>
       <c r="G2" t="n">
         <v>0.8265</v>
@@ -610,13 +610,13 @@
         <v>3.1255</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.9684</v>
+        <v>-0.3026</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7784</v>
+        <v>-0.6574</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1899</v>
+        <v>0.3548</v>
       </c>
       <c r="V2" t="n">
         <v>3.3787</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1931</v>
+        <v>3.3448</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0266</v>
+        <v>0.5251</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1665</v>
+        <v>2.8197</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5173</v>
+        <v>2.4004</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1665</v>
+        <v>-0.06859999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3508</v>
+        <v>2.469</v>
       </c>
       <c r="J3" t="n">
-        <v>1.8718</v>
+        <v>2.7597</v>
       </c>
       <c r="K3" t="n">
-        <v>1.925</v>
+        <v>0.9644</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.0533</v>
+        <v>1.7953</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3544</v>
+        <v>-0.3593</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7585</v>
+        <v>-1.033</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4041</v>
+        <v>0.6737</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1488</v>
+        <v>-1.9534</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1721</v>
+        <v>2.5395</v>
       </c>
       <c r="S3" t="n">
-        <v>2.0432</v>
+        <v>0.3583</v>
       </c>
       <c r="T3" t="n">
-        <v>1.4171</v>
+        <v>-0.2812</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6261</v>
+        <v>0.6395999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8865</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8482</v>
+        <v>2.9233</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.453</v>
+        <v>0.7326</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3012</v>
+        <v>2.1906</v>
       </c>
       <c r="G4" t="n">
-        <v>1.658</v>
+        <v>0.8813</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4454</v>
+        <v>0.8414</v>
       </c>
       <c r="I4" t="n">
-        <v>2.1034</v>
+        <v>0.0399</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4876</v>
+        <v>0.7568</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.7163</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8902</v>
+        <v>0.0405</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1705</v>
+        <v>0.1245</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0427</v>
+        <v>0.1251</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2132</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9534</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1721</v>
+        <v>-1.9534</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1255</v>
+        <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7874</v>
+        <v>0.6596</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1043</v>
+        <v>0.1562</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8918</v>
+        <v>0.5034</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.5507</v>
+        <v>1.7731</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6642</v>
+        <v>1.7731</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7938</v>
+        <v>2.194</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1621</v>
+        <v>1.1365</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9559</v>
+        <v>1.0575</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4004</v>
+        <v>1.5173</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.06859999999999999</v>
+        <v>1.1665</v>
       </c>
       <c r="I5" t="n">
-        <v>2.469</v>
+        <v>0.3508</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7597</v>
+        <v>1.8718</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9644</v>
+        <v>1.925</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7953</v>
+        <v>-0.0533</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3593</v>
+        <v>-0.3544</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.033</v>
+        <v>-0.7585</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6737</v>
+        <v>0.4041</v>
       </c>
       <c r="P5" t="n">
-        <v>0.586</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>-2.1488</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5395</v>
+        <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1926</v>
+        <v>1.0441</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9684</v>
+        <v>0.527</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7756999999999999</v>
+        <v>0.5172</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.8865</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.454</v>
+        <v>2.0888</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0455</v>
+        <v>-0.4422</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4085</v>
+        <v>2.5311</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8813</v>
+        <v>-1.4605</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8414</v>
+        <v>-1.7035</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0399</v>
+        <v>0.243</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7568</v>
+        <v>-1.1565</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7163</v>
+        <v>-0.591</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0405</v>
+        <v>-0.5655</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1245</v>
+        <v>-0.304</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1251</v>
+        <v>-1.1125</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.8085</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.3907</v>
+        <v>2.3441</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5627</v>
+        <v>2.3441</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1903</v>
+        <v>0.0963</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5309</v>
+        <v>-0.3946</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.491</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7731</v>
+        <v>1.1089</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7731</v>
+        <v>1.1089</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4323</v>
+        <v>1.9286</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0171</v>
+        <v>0.7288</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4494</v>
+        <v>1.1998</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4605</v>
+        <v>0.8645</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7035</v>
+        <v>0.7836</v>
       </c>
       <c r="I7" t="n">
-        <v>0.243</v>
+        <v>0.0809</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.1565</v>
+        <v>0.9495</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.591</v>
+        <v>1.0028</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5655</v>
+        <v>-0.0533</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.304</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1125</v>
+        <v>-0.2192</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8085</v>
+        <v>0.1342</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3441</v>
+        <v>0.7814</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R7" t="n">
-        <v>2.3441</v>
+        <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4397</v>
+        <v>0.2827</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0305</v>
+        <v>-0.0254</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4093</v>
+        <v>0.308</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1089</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1089</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1325</v>
+        <v>1.9074</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0417</v>
+        <v>-1.0398</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0908</v>
+        <v>2.9471</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8645</v>
+        <v>1.658</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7836</v>
+        <v>-0.4454</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0809</v>
+        <v>2.1034</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9495</v>
+        <v>1.4876</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0028</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.0533</v>
+        <v>0.8902</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0.1705</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2192</v>
+        <v>-1.0427</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1342</v>
+        <v>1.2132</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7814</v>
+        <v>1.9534</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9767</v>
+        <v>3.1255</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5134</v>
+        <v>-0.1534</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7125</v>
+        <v>-0.6911</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1991</v>
+        <v>0.5377</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.5507</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8111</v>
+        <v>1.2705</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9862</v>
+        <v>-0.6629</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7972</v>
+        <v>1.9334</v>
       </c>
       <c r="G9" t="n">
         <v>0.3021</v>
@@ -1156,13 +1156,13 @@
         <v>1.3674</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8584000000000001</v>
+        <v>-0.3989</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8335</v>
+        <v>-0.5103</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0248</v>
+        <v>0.1113</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5192</v>
+        <v>-0.4181</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0401</v>
+        <v>0.0611</v>
       </c>
       <c r="F10" t="n">
         <v>-0.4792</v>
@@ -1234,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0605</v>
+        <v>0.0406</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0605</v>
+        <v>0.0406</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7741</v>
+        <v>-0.6729000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.09030000000000001</v>
+        <v>0.0109</v>
       </c>
       <c r="F11" t="n">
         <v>-0.6838</v>
@@ -1312,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0605</v>
+        <v>0.0406</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0605</v>
+        <v>0.0406</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4394</v>
+        <v>-0.84</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.8209</v>
+        <v>-4.1943</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3816</v>
+        <v>3.3543</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1005</v>
@@ -1390,13 +1390,13 @@
         <v>3.3208</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7528</v>
+        <v>-0.1534</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.392</v>
+        <v>-0.7654</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6392</v>
+        <v>0.612</v>
       </c>
       <c r="V12" t="n">
         <v>1.2186</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.6921</v>
+        <v>-5.6389</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.4227</v>
+        <v>-6.3423</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7306</v>
+        <v>0.7034</v>
       </c>
       <c r="G13" t="n">
         <v>-4.125</v>
@@ -1468,13 +1468,13 @@
         <v>0.9767</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3863</v>
+        <v>0.4395</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1432</v>
+        <v>0.2236</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2431</v>
+        <v>0.2159</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>13.4071</v>
+        <v>14.9202</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.335599999999999</v>
+        <v>-5.822500000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>20.7427</v>
+        <v>20.7426</v>
       </c>
       <c r="G14" t="n">
         <v>0.2559999999999985</v>
       </c>
       <c r="H14" t="n">
-        <v>-7.1631</v>
+        <v>-7.163099999999999</v>
       </c>
       <c r="I14" t="n">
         <v>7.419</v>
@@ -1537,7 +1537,7 @@
         <v>6.062899999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>6.836899999999998</v>
+        <v>6.8369</v>
       </c>
       <c r="Q14" t="n">
         <v>-13.6739</v>
@@ -1546,10 +1546,10 @@
         <v>20.511</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4403000000000002</v>
+        <v>1.9534</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.850200000000001</v>
+        <v>-2.3374</v>
       </c>
       <c r="U14" t="n">
         <v>4.2909</v>
@@ -1558,7 +1558,7 @@
         <v>5.873699999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>7.314599999999999</v>
+        <v>7.3146</v>
       </c>
       <c r="X14" t="n">
         <v>-1.4409</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3607</v>
+        <v>2.2933</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6947</v>
+        <v>1.4925</v>
       </c>
       <c r="F15" t="n">
-        <v>0.666</v>
+        <v>0.8008</v>
       </c>
       <c r="G15" t="n">
         <v>5.8217</v>
@@ -1624,13 +1624,13 @@
         <v>2.1488</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2972</v>
+        <v>-0.3646</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4758</v>
+        <v>-0.6781</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1786</v>
+        <v>0.3135</v>
       </c>
       <c r="V15" t="n">
         <v>-2.3824</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0385</v>
+        <v>0.5717</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4755</v>
+        <v>0.1721</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.3996</v>
       </c>
       <c r="G16" t="n">
         <v>0.0848</v>
@@ -1702,13 +1702,13 @@
         <v>0.3907</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8401999999999999</v>
+        <v>0.3735</v>
       </c>
       <c r="T16" t="n">
-        <v>0.311</v>
+        <v>0.0076</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5293</v>
+        <v>0.3658</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2772</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7085</v>
+        <v>0.3622</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6774</v>
+        <v>-1.7785</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3859</v>
+        <v>2.1408</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4404</v>
@@ -1780,13 +1780,13 @@
         <v>1.9534</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1722</v>
+        <v>-0.1741</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4153</v>
+        <v>-0.5164</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5875</v>
+        <v>0.3424</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0443</v>
+        <v>0.2812</v>
       </c>
       <c r="E18" t="n">
         <v>-0.5875</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5433</v>
+        <v>0.8687</v>
       </c>
       <c r="G18" t="n">
         <v>-0.127</v>
@@ -1858,13 +1858,13 @@
         <v>0.9767</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0269</v>
+        <v>0.2985</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1732</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1463</v>
+        <v>0.4718</v>
       </c>
       <c r="V18" t="n">
         <v>0.1097</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7955</v>
+        <v>-1.3555</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2084</v>
+        <v>-2.4407</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5871</v>
+        <v>1.0852</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.9846</v>
+        <v>1.1378</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3623</v>
+        <v>1.5168</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3468</v>
+        <v>-0.379</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2251</v>
+        <v>1.6379</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0422</v>
+        <v>1.4761</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2673</v>
+        <v>0.1619</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7595</v>
+        <v>-0.5002</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3201</v>
+        <v>0.0407</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0795</v>
+        <v>-0.5409</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1953</v>
+        <v>-0.586</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1721</v>
+        <v>2.3441</v>
       </c>
       <c r="S21" t="n">
-        <v>1.2123</v>
+        <v>-0.4113</v>
       </c>
       <c r="T21" t="n">
-        <v>0.9933999999999999</v>
+        <v>-1.1485</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2189</v>
+        <v>0.7371</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>-1.4959</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3148</v>
+        <v>-2.3722</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.0474</v>
+        <v>-2.2195</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7325</v>
+        <v>-0.1527</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1378</v>
+        <v>-1.9846</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5168</v>
+        <v>0.3623</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.379</v>
+        <v>-2.3468</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6379</v>
+        <v>-1.2251</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4761</v>
+        <v>0.0422</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1619</v>
+        <v>-1.2673</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5002</v>
+        <v>-0.7595</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0407</v>
+        <v>0.3201</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5409</v>
+        <v>-1.0795</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3441</v>
+        <v>1.1721</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3707</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.7552</v>
+        <v>-0.0177</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3844</v>
+        <v>0.6533</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.4959</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4588</v>
+        <v>-2.7155</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5825</v>
+        <v>-3.7847</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1237</v>
+        <v>1.0692</v>
       </c>
       <c r="G23" t="n">
         <v>-0.8756</v>
@@ -2248,13 +2248,13 @@
         <v>0.586</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6708</v>
+        <v>0.4141</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2504</v>
+        <v>0.0482</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4203</v>
+        <v>0.3658</v>
       </c>
       <c r="V23" t="n">
         <v>-0.8865</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2678</v>
+        <v>-2.9334</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9396</v>
+        <v>-2.3329</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3282</v>
+        <v>-0.6005</v>
       </c>
       <c r="G24" t="n">
         <v>0.3035</v>
@@ -2326,13 +2326,13 @@
         <v>1.9534</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6411</v>
+        <v>-0.3068</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.5736</v>
+        <v>-0.9669</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9325</v>
+        <v>0.6601</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.4</v>
+        <v>-6.6313</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.911</v>
+        <v>-9.3043</v>
       </c>
       <c r="F25" t="n">
-        <v>2.511</v>
+        <v>2.673</v>
       </c>
       <c r="G25" t="n">
         <v>-3.9426</v>
@@ -2404,13 +2404,13 @@
         <v>2.1488</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9999</v>
+        <v>-0.2311</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.4525</v>
+        <v>-0.8459</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4527</v>
+        <v>0.6147</v>
       </c>
       <c r="V25" t="n">
         <v>0.2772</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-13.4071</v>
+        <v>-12.7331</v>
       </c>
       <c r="E26" t="n">
-        <v>-20.7426</v>
+        <v>-20.7425</v>
       </c>
       <c r="F26" t="n">
-        <v>7.335599999999999</v>
+        <v>8.009600000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-0.2559999999999998</v>
@@ -2482,13 +2482,13 @@
         <v>13.674</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.4403000000000001</v>
+        <v>0.2338</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.2908</v>
+        <v>-4.2909</v>
       </c>
       <c r="U26" t="n">
-        <v>3.8505</v>
+        <v>4.5245</v>
       </c>
       <c r="V26" t="n">
         <v>-5.8737</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484217_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484217_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -782,6 +797,11 @@
       </c>
       <c r="X4" t="n">
         <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-0.8865</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,11 +1213,16 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SERRA SÀNCHEZ</t>
+          <t>J. SERRA SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1250,6 +1295,11 @@
       </c>
       <c r="X10" t="n">
         <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-1.4409</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,11 +1707,16 @@
       <c r="X15" t="n">
         <v>-2.0503</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. ANCISO SANTANDER</t>
+          <t>P. CABAÑERO PUERTAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5717</v>
+        <v>1.5349</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1721</v>
+        <v>1.5349</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3996</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0848</v>
+        <v>1.5349</v>
       </c>
       <c r="H16" t="n">
-        <v>0.449</v>
+        <v>1.5349</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3642</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1645</v>
+        <v>1.5349</v>
       </c>
       <c r="K16" t="n">
-        <v>0.7982</v>
+        <v>1.5349</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.07969999999999999</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3492</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2694</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3735</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0076</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3658</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. CASADO FAJO</t>
+          <t>S. ANCISO SANTANDER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3622</v>
+        <v>0.5717</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.7785</v>
+        <v>0.1721</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1408</v>
+        <v>0.3996</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4404</v>
+        <v>0.0848</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3827</v>
+        <v>0.449</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.3642</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2854</v>
+        <v>0.1645</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9414</v>
+        <v>0.7982</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2268</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.155</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5587</v>
+        <v>-0.3492</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4037</v>
+        <v>0.2694</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9534</v>
+        <v>0.3907</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1741</v>
+        <v>0.3735</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5164</v>
+        <v>0.0076</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3424</v>
+        <v>0.3658</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. CASTELLO LOGROÑO</t>
+          <t>M. CASADO FAJO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2812</v>
+        <v>0.3622</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5875</v>
+        <v>-1.7785</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8687</v>
+        <v>2.1408</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.127</v>
+        <v>-0.4404</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0325</v>
+        <v>0.3827</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0946</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5624</v>
+        <v>-0.2854</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0179</v>
+        <v>0.9414</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5803</v>
+        <v>-1.2268</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6895</v>
+        <v>-0.155</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0146</v>
+        <v>-0.5587</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.4037</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9767</v>
+        <v>1.9534</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2985</v>
+        <v>-0.1741</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1732</v>
+        <v>-0.5164</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4718</v>
+        <v>0.3424</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1097</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.1097</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. ABAD CALAVIA</t>
+          <t>J. CASTELLO LOGROÑO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,37 +1977,37 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0494</v>
+        <v>0.307</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0205</v>
+        <v>0.307</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0698</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0494</v>
+        <v>0.307</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0494</v>
+        <v>0.307</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0205</v>
+        <v>0.307</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0205</v>
+        <v>0.307</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0698</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0698</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -1952,12 +2038,17 @@
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ LAFUENTE</t>
+          <t>J. CASTELLO LOGRONO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1842</v>
+        <v>-0.0258</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0205</v>
+        <v>-0.8945</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2047</v>
+        <v>0.8687</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1842</v>
+        <v>-0.434</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1842</v>
+        <v>-0.3395</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-0.0946</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0205</v>
+        <v>0.2554</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0205</v>
+        <v>-0.3249</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.5803</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2047</v>
+        <v>-0.6895</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2047</v>
+        <v>-0.0146</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>0.2985</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>-0.1732</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>0.4718</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.1097</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.1097</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. CABAÑERO PUERTAS</t>
+          <t>D. ABAD CALAVIA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3555</v>
+        <v>-0.0494</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4407</v>
+        <v>0.0205</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0852</v>
+        <v>-0.0698</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1378</v>
+        <v>-0.0494</v>
       </c>
       <c r="H21" t="n">
-        <v>1.5168</v>
+        <v>-0.0494</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.379</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6379</v>
+        <v>0.0205</v>
       </c>
       <c r="K21" t="n">
-        <v>1.4761</v>
+        <v>0.0205</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1619</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5002</v>
+        <v>-0.0698</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0407</v>
+        <v>-0.0698</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5409</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4113</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1485</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7371</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. BORGES PINO</t>
+          <t>D. FERNANDEZ LAFUENTE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3722</v>
+        <v>-0.1842</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2195</v>
+        <v>0.0205</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.1527</v>
+        <v>-0.2047</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.9846</v>
+        <v>-0.1842</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3623</v>
+        <v>-0.1842</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.3468</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2251</v>
+        <v>0.0205</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0422</v>
+        <v>0.0205</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.2673</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7595</v>
+        <v>-0.2047</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3201</v>
+        <v>-0.2047</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0795</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6356000000000001</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0177</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6533</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. HERMOSO HERMIDA</t>
+          <t>R. BORGES PINO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7155</v>
+        <v>-2.3722</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7847</v>
+        <v>-2.2195</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0692</v>
+        <v>-0.1527</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.8756</v>
+        <v>-1.9846</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.1857</v>
+        <v>0.3623</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3101</v>
+        <v>-2.3468</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8795</v>
+        <v>-1.2251</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2459</v>
+        <v>0.0422</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-1.2673</v>
       </c>
       <c r="M23" t="n">
-        <v>1.0039</v>
+        <v>-0.7595</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0601</v>
+        <v>0.3201</v>
       </c>
       <c r="O23" t="n">
-        <v>0.9437</v>
+        <v>-1.0795</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4141</v>
+        <v>0.6356000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0482</v>
+        <v>-0.0177</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3658</v>
+        <v>0.6533</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.8865</v>
+        <v>-1.2186</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.8865</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. GEORGIOU</t>
+          <t>R. HERMOSO HERMIDA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.9334</v>
+        <v>-2.7155</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3329</v>
+        <v>-3.7847</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6005</v>
+        <v>1.0692</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3035</v>
+        <v>-0.8756</v>
       </c>
       <c r="H24" t="n">
-        <v>1.8672</v>
+        <v>-1.1857</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.5638</v>
+        <v>0.3101</v>
       </c>
       <c r="J24" t="n">
-        <v>2.0217</v>
+        <v>-1.8795</v>
       </c>
       <c r="K24" t="n">
-        <v>2.9099</v>
+        <v>-1.2459</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.8883</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.7182</v>
+        <v>1.0039</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0427</v>
+        <v>0.0601</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6755</v>
+        <v>0.9437</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.9301</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.8836</v>
+        <v>-1.9534</v>
       </c>
       <c r="R24" t="n">
-        <v>1.9534</v>
+        <v>0.586</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.3068</v>
+        <v>0.4141</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9669</v>
+        <v>0.0482</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6601</v>
+        <v>0.3658</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
       <c r="W24" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4959</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. MILLS NALES</t>
+          <t>P. CABANERO PUERTAS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.6313</v>
+        <v>-2.8904</v>
       </c>
       <c r="E25" t="n">
-        <v>-9.3043</v>
+        <v>-3.9756</v>
       </c>
       <c r="F25" t="n">
-        <v>2.673</v>
+        <v>1.0852</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.9426</v>
+        <v>-0.3971</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.8392</v>
+        <v>-0.0181</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.1034</v>
+        <v>-0.379</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.8521</v>
+        <v>0.103</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.7499</v>
+        <v>-0.0589</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.1022</v>
+        <v>0.1619</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.09039999999999999</v>
+        <v>-0.5002</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0893</v>
+        <v>0.0407</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.0012</v>
+        <v>-0.5409</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.7348</v>
+        <v>-0.586</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.8836</v>
+        <v>-2.9301</v>
       </c>
       <c r="R25" t="n">
-        <v>2.1488</v>
+        <v>2.3441</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2311</v>
+        <v>-0.4113</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8459</v>
+        <v>-1.1485</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6147</v>
+        <v>0.7371</v>
       </c>
       <c r="V25" t="n">
-        <v>0.2772</v>
+        <v>-1.4959</v>
       </c>
       <c r="W25" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>G. GEORGIOU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,68 +2558,235 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
+        <v>-2.9334</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-2.3329</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.6005</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.8672</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.5638</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.0217</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.9099</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.8883</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.7182</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.0427</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.6755</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-4.8836</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.3068</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.9669</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.6601</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>D. MILLS NALES</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-6.6313</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-9.3043</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2.673</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-3.9426</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.8392</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-2.1034</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-3.8521</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-1.7499</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-2.1022</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.09039999999999999</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.0893</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-2.7348</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-4.8836</v>
+      </c>
+      <c r="R27" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.2311</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.8459</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.6147</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484217_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FRIVALCA LA MUELA</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
         <v>-12.7331</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E28" t="n">
         <v>-20.7425</v>
       </c>
-      <c r="F26" t="n">
-        <v>8.009600000000001</v>
-      </c>
-      <c r="G26" t="n">
-        <v>-0.2559999999999998</v>
-      </c>
-      <c r="H26" t="n">
+      <c r="F28" t="n">
+        <v>8.009599999999999</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-0.2559999999999989</v>
+      </c>
+      <c r="H28" t="n">
         <v>7.163</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I28" t="n">
         <v>-7.4191</v>
       </c>
-      <c r="J26" t="n">
-        <v>2.618200000000001</v>
-      </c>
-      <c r="K26" t="n">
-        <v>8.681199999999999</v>
-      </c>
-      <c r="L26" t="n">
-        <v>-6.0629</v>
-      </c>
-      <c r="M26" t="n">
+      <c r="J28" t="n">
+        <v>2.6182</v>
+      </c>
+      <c r="K28" t="n">
+        <v>8.681099999999999</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-6.062899999999999</v>
+      </c>
+      <c r="M28" t="n">
         <v>-2.8742</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N28" t="n">
         <v>-1.5182</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O28" t="n">
         <v>-1.3562</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P28" t="n">
         <v>-6.837</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q28" t="n">
         <v>-20.5109</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R28" t="n">
         <v>13.674</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S28" t="n">
         <v>0.2338</v>
       </c>
-      <c r="T26" t="n">
-        <v>-4.2909</v>
-      </c>
-      <c r="U26" t="n">
+      <c r="T28" t="n">
+        <v>-4.290900000000001</v>
+      </c>
+      <c r="U28" t="n">
         <v>4.5245</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V28" t="n">
         <v>-5.8737</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W28" t="n">
         <v>1.441</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X28" t="n">
         <v>-7.314699999999999</v>
       </c>
+      <c r="Y28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
